--- a/apps/api/templates/waybill-esm2.xlsx
+++ b/apps/api/templates/waybill-esm2.xlsx
@@ -10882,7 +10882,7 @@
     </row>
     <row r="148" customFormat="false" ht="11.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="201">
+  <mergeCells count="202">
     <mergeCell ref="T2:AL3"/>
     <mergeCell ref="BF2:BG3"/>
     <mergeCell ref="BV2:CF2"/>
@@ -11084,6 +11084,7 @@
     <mergeCell ref="U147:X147"/>
     <mergeCell ref="AM2:BE3"/>
     <mergeCell ref="BH2:BO3"/>
+    <mergeCell ref="BI11:BJ11"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0" footer="0"/>
